--- a/temp_doc/MAPEL- CODING X.xlsx
+++ b/temp_doc/MAPEL- CODING X.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725866B1-A3A2-1C4E-93E9-6F8140E50976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D7D3F7-128E-5E49-BD45-0845F66A2625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>id_mapel</t>
   </si>
@@ -75,6 +76,36 @@
   </si>
   <si>
     <t>CODING ( X DKV )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X AKL 1 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X AKL 2 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X PM )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( X DKV )</t>
   </si>
 </sst>
 </file>
@@ -601,65 +632,205 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="20" x14ac:dyDescent="0.2">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" ht="20" x14ac:dyDescent="0.2">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" ht="20" x14ac:dyDescent="0.2">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" ht="20" x14ac:dyDescent="0.2">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="20" x14ac:dyDescent="0.2">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="2:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="2:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="2:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="2:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12">
+        <v>1001</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13">
+        <v>1002</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14">
+        <v>1003</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15">
+        <v>1004</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1015</v>
+      </c>
+      <c r="B16">
+        <v>1005</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1016</v>
+      </c>
+      <c r="B17">
+        <v>1006</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1017</v>
+      </c>
+      <c r="B18">
+        <v>1007</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1018</v>
+      </c>
+      <c r="B19">
+        <v>1008</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1019</v>
+      </c>
+      <c r="B20">
+        <v>1009</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1020</v>
+      </c>
+      <c r="B21">
+        <v>1010</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="2:2" ht="20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="20" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D615468D-DF70-3D42-98BB-F85C9840DA85}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/temp_doc/MAPEL- CODING X.xlsx
+++ b/temp_doc/MAPEL- CODING X.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D7D3F7-128E-5E49-BD45-0845F66A2625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B30394-831F-354E-B593-AC3BF01F8A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$39</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
   <si>
     <t>id_mapel</t>
   </si>
@@ -106,25 +109,106 @@
   </si>
   <si>
     <t>MATEMATIKA ( X DKV )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA</t>
+  </si>
+  <si>
+    <t>XI AKL 1</t>
+  </si>
+  <si>
+    <t>XI AKL 2</t>
+  </si>
+  <si>
+    <t>XI PM</t>
+  </si>
+  <si>
+    <t>XI MPLB 1</t>
+  </si>
+  <si>
+    <t>XI MPLB 2</t>
+  </si>
+  <si>
+    <t>XI TJKT 1</t>
+  </si>
+  <si>
+    <t>XI TJKT 2</t>
+  </si>
+  <si>
+    <t>XI TJKT 3</t>
+  </si>
+  <si>
+    <t>XI DKV</t>
+  </si>
+  <si>
+    <t>CODING</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI AKL 1 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI AKL 2 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI PM )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>MATEMATIKA ( XI DKV )</t>
+  </si>
+  <si>
+    <t>CODING ( XI AKL 1 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI AKL 2 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI PM )</t>
+  </si>
+  <si>
+    <t>CODING ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>CODING ( XI DKV )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF858796"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -154,10 +238,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E4DC37-752B-FA41-9A64-68D7A3795B3C}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -522,7 +605,7 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -534,7 +617,7 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -546,7 +629,7 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -558,7 +641,7 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -570,7 +653,7 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -582,7 +665,7 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -594,7 +677,7 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -606,7 +689,7 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -618,7 +701,7 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -630,7 +713,7 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -742,35 +825,203 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B31" s="1"/>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1021</v>
+      </c>
+      <c r="B22">
+        <v>1011</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1022</v>
+      </c>
+      <c r="B23">
+        <v>1012</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1023</v>
+      </c>
+      <c r="B24">
+        <v>1013</v>
+      </c>
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25">
+        <v>1014</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>1025</v>
+      </c>
+      <c r="B26">
+        <v>1015</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>1026</v>
+      </c>
+      <c r="B27">
+        <v>1016</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1027</v>
+      </c>
+      <c r="B28">
+        <v>1017</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1028</v>
+      </c>
+      <c r="B29">
+        <v>1018</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1029</v>
+      </c>
+      <c r="B30">
+        <v>1019</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>1030</v>
+      </c>
+      <c r="B31">
+        <v>1011</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>1031</v>
+      </c>
+      <c r="B32">
+        <v>1012</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>1032</v>
+      </c>
+      <c r="B33">
+        <v>1013</v>
+      </c>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>1033</v>
+      </c>
+      <c r="B34">
+        <v>1014</v>
+      </c>
+      <c r="C34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>1034</v>
+      </c>
+      <c r="B35">
+        <v>1015</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>1035</v>
+      </c>
+      <c r="B36">
+        <v>1016</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>1036</v>
+      </c>
+      <c r="B37">
+        <v>1017</v>
+      </c>
+      <c r="C37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>1037</v>
+      </c>
+      <c r="B38">
+        <v>1018</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>1038</v>
+      </c>
+      <c r="B39">
+        <v>1019</v>
+      </c>
+      <c r="C39" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -779,57 +1030,226 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D615468D-DF70-3D42-98BB-F85C9840DA85}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="str">
+        <f>CONCATENATE(A1," ( ",B1," )")</f>
+        <v>MATEMATIKA ( XI AKL 1 )</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C18" si="0">CONCATENATE(A2," ( ",B2," )")</f>
+        <v>MATEMATIKA ( XI AKL 2 )</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI PM )</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI MPLB 1 )</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI MPLB 2 )</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI TJKT 1 )</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI TJKT 2 )</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI TJKT 3 )</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>MATEMATIKA ( XI DKV )</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI AKL 1 )</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI AKL 2 )</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI PM )</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI MPLB 1 )</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI MPLB 2 )</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI TJKT 1 )</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI TJKT 2 )</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI TJKT 3 )</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING ( XI DKV )</v>
       </c>
     </row>
   </sheetData>

--- a/temp_doc/MAPEL- CODING X.xlsx
+++ b/temp_doc/MAPEL- CODING X.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B30394-831F-354E-B593-AC3BF01F8A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34F21A5-9586-884B-9565-7948D03331D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>id_mapel</t>
   </si>
@@ -81,36 +81,6 @@
     <t>CODING ( X DKV )</t>
   </si>
   <si>
-    <t>MATEMATIKA ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X PM )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X MPLB 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X MPLB 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X TJKT 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X TJKT 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X TJKT 3 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X TJKT 4 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X DKV )</t>
-  </si>
-  <si>
     <t>MATEMATIKA</t>
   </si>
   <si>
@@ -142,33 +112,6 @@
   </si>
   <si>
     <t>CODING</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI PM )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI MPLB 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI MPLB 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI TJKT 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI TJKT 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI TJKT 3 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI DKV )</t>
   </si>
   <si>
     <t>CODING ( XI AKL 1 )</t>
@@ -575,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E4DC37-752B-FA41-9A64-68D7A3795B3C}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -717,310 +660,101 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>1030</v>
+      </c>
+      <c r="B12">
         <v>1011</v>
       </c>
-      <c r="B12">
-        <v>1001</v>
-      </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
+        <v>1031</v>
+      </c>
+      <c r="B13">
         <v>1012</v>
       </c>
-      <c r="B13">
-        <v>1002</v>
-      </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
+        <v>1032</v>
+      </c>
+      <c r="B14">
         <v>1013</v>
       </c>
-      <c r="B14">
-        <v>1003</v>
-      </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
+        <v>1033</v>
+      </c>
+      <c r="B15">
         <v>1014</v>
       </c>
-      <c r="B15">
-        <v>1004</v>
-      </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
+        <v>1034</v>
+      </c>
+      <c r="B16">
         <v>1015</v>
       </c>
-      <c r="B16">
-        <v>1005</v>
-      </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>1035</v>
+      </c>
+      <c r="B17">
         <v>1016</v>
       </c>
-      <c r="B17">
-        <v>1006</v>
-      </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>1036</v>
+      </c>
+      <c r="B18">
         <v>1017</v>
       </c>
-      <c r="B18">
-        <v>1007</v>
-      </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
+        <v>1037</v>
+      </c>
+      <c r="B19">
         <v>1018</v>
       </c>
-      <c r="B19">
-        <v>1008</v>
-      </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
+        <v>1038</v>
+      </c>
+      <c r="B20">
         <v>1019</v>
       </c>
-      <c r="B20">
-        <v>1009</v>
-      </c>
       <c r="C20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>1020</v>
-      </c>
-      <c r="B21">
-        <v>1010</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>1021</v>
-      </c>
-      <c r="B22">
-        <v>1011</v>
-      </c>
-      <c r="C22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>1022</v>
-      </c>
-      <c r="B23">
-        <v>1012</v>
-      </c>
-      <c r="C23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>1023</v>
-      </c>
-      <c r="B24">
-        <v>1013</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>1024</v>
-      </c>
-      <c r="B25">
-        <v>1014</v>
-      </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>1025</v>
-      </c>
-      <c r="B26">
-        <v>1015</v>
-      </c>
-      <c r="C26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>1026</v>
-      </c>
-      <c r="B27">
-        <v>1016</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>1027</v>
-      </c>
-      <c r="B28">
-        <v>1017</v>
-      </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>1028</v>
-      </c>
-      <c r="B29">
-        <v>1018</v>
-      </c>
-      <c r="C29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>1029</v>
-      </c>
-      <c r="B30">
-        <v>1019</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>1030</v>
-      </c>
-      <c r="B31">
-        <v>1011</v>
-      </c>
-      <c r="C31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>1031</v>
-      </c>
-      <c r="B32">
-        <v>1012</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>1032</v>
-      </c>
-      <c r="B33">
-        <v>1013</v>
-      </c>
-      <c r="C33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>1033</v>
-      </c>
-      <c r="B34">
-        <v>1014</v>
-      </c>
-      <c r="C34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>1034</v>
-      </c>
-      <c r="B35">
-        <v>1015</v>
-      </c>
-      <c r="C35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>1035</v>
-      </c>
-      <c r="B36">
-        <v>1016</v>
-      </c>
-      <c r="C36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>1036</v>
-      </c>
-      <c r="B37">
-        <v>1017</v>
-      </c>
-      <c r="C37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>1037</v>
-      </c>
-      <c r="B38">
-        <v>1018</v>
-      </c>
-      <c r="C38" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>1038</v>
-      </c>
-      <c r="B39">
-        <v>1019</v>
-      </c>
-      <c r="C39" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1038,10 +772,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C1" t="str">
         <f>CONCATENATE(A1," ( ",B1," )")</f>
@@ -1050,10 +784,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" ref="C2:C18" si="0">CONCATENATE(A2," ( ",B2," )")</f>
@@ -1062,10 +796,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
@@ -1074,10 +808,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -1086,10 +820,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -1098,10 +832,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -1110,10 +844,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -1122,10 +856,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -1134,10 +868,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -1146,10 +880,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -1158,10 +892,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -1170,10 +904,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -1182,10 +916,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -1194,10 +928,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -1206,10 +940,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -1218,10 +952,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -1230,10 +964,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -1242,10 +976,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>

--- a/temp_doc/MAPEL- CODING X.xlsx
+++ b/temp_doc/MAPEL- CODING X.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34F21A5-9586-884B-9565-7948D03331D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2F9DA5-BBBB-8648-AC4D-B5F11026C13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
   <si>
     <t>id_mapel</t>
   </si>
@@ -51,36 +51,6 @@
     <t>nama_mapel</t>
   </si>
   <si>
-    <t>CODING ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>CODING ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>CODING ( X PM )</t>
-  </si>
-  <si>
-    <t>CODING ( X MPLB 1 )</t>
-  </si>
-  <si>
-    <t>CODING ( X MPLB 2 )</t>
-  </si>
-  <si>
-    <t>CODING ( X TJKT 1 )</t>
-  </si>
-  <si>
-    <t>CODING ( X TJKT 2 )</t>
-  </si>
-  <si>
-    <t>CODING ( X TJKT 3 )</t>
-  </si>
-  <si>
-    <t>CODING ( X TJKT 4 )</t>
-  </si>
-  <si>
-    <t>CODING ( X DKV )</t>
-  </si>
-  <si>
     <t>MATEMATIKA</t>
   </si>
   <si>
@@ -114,31 +84,34 @@
     <t>CODING</t>
   </si>
   <si>
-    <t>CODING ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI PM )</t>
-  </si>
-  <si>
-    <t>CODING ( XI MPLB 1 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI MPLB 2 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI TJKT 1 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI TJKT 2 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI TJKT 3 )</t>
-  </si>
-  <si>
-    <t>CODING ( XI DKV )</t>
+    <t>CODING &amp; AI ( X AKL 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X AKL 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X PM )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X DKV )</t>
   </si>
 </sst>
 </file>
@@ -518,13 +491,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E4DC37-752B-FA41-9A64-68D7A3795B3C}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -546,7 +521,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -558,7 +533,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -570,7 +545,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -582,7 +557,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1"/>
     </row>
@@ -594,7 +569,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -606,7 +581,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -618,7 +593,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -630,7 +605,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -642,7 +617,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -654,108 +629,9 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1030</v>
-      </c>
-      <c r="B12">
-        <v>1011</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1031</v>
-      </c>
-      <c r="B13">
-        <v>1012</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1032</v>
-      </c>
-      <c r="B14">
-        <v>1013</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1033</v>
-      </c>
-      <c r="B15">
-        <v>1014</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>1034</v>
-      </c>
-      <c r="B16">
-        <v>1015</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>1035</v>
-      </c>
-      <c r="B17">
-        <v>1016</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>1036</v>
-      </c>
-      <c r="B18">
-        <v>1017</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>1037</v>
-      </c>
-      <c r="B19">
-        <v>1018</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>1038</v>
-      </c>
-      <c r="B20">
-        <v>1019</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -772,10 +648,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" t="str">
         <f>CONCATENATE(A1," ( ",B1," )")</f>
@@ -784,10 +660,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" ref="C2:C18" si="0">CONCATENATE(A2," ( ",B2," )")</f>
@@ -796,10 +672,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
@@ -808,10 +684,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -820,10 +696,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -832,10 +708,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -844,10 +720,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -856,10 +732,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -868,10 +744,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -880,10 +756,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -892,10 +768,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -904,10 +780,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -916,10 +792,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -928,10 +804,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -940,10 +816,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -952,10 +828,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -964,10 +840,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -976,10 +852,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>

--- a/temp_doc/MAPEL- CODING X.xlsx
+++ b/temp_doc/MAPEL- CODING X.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2F9DA5-BBBB-8648-AC4D-B5F11026C13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623C32B8-4B38-B347-8BD8-503CF1361A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>id_mapel</t>
   </si>
@@ -112,6 +112,123 @@
   </si>
   <si>
     <t>CODING &amp; AI ( X DKV )</t>
+  </si>
+  <si>
+    <t>X AKL 1</t>
+  </si>
+  <si>
+    <t>X AKL 2</t>
+  </si>
+  <si>
+    <t>X PM</t>
+  </si>
+  <si>
+    <t>X MPLB 1</t>
+  </si>
+  <si>
+    <t>X MPLB 2</t>
+  </si>
+  <si>
+    <t>X TJKT 1</t>
+  </si>
+  <si>
+    <t>X TJKT 2</t>
+  </si>
+  <si>
+    <t>X TJKT 3</t>
+  </si>
+  <si>
+    <t>X TJKT 4</t>
+  </si>
+  <si>
+    <t>X DKV</t>
+  </si>
+  <si>
+    <t>XI TJKT 4</t>
+  </si>
+  <si>
+    <t>XII AKL 1</t>
+  </si>
+  <si>
+    <t>XII AKL 2</t>
+  </si>
+  <si>
+    <t>XII PM</t>
+  </si>
+  <si>
+    <t>XII MPLB 1</t>
+  </si>
+  <si>
+    <t>XII MPLB 2</t>
+  </si>
+  <si>
+    <t>XII TJKT 1</t>
+  </si>
+  <si>
+    <t>XII TJKT 2</t>
+  </si>
+  <si>
+    <t>XII TJKT 3</t>
+  </si>
+  <si>
+    <t>XII DKV</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI AKL 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI AKL 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI PM )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI TJKT 4 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XI DKV )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII AKL 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII AKL 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII PM )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII MPLB 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII MPLB 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII TJKT 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII TJKT 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII TJKT 3 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( XII DKV )</t>
   </si>
 </sst>
 </file>
@@ -491,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E4DC37-752B-FA41-9A64-68D7A3795B3C}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -502,7 +619,7 @@
     <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -523,9 +640,18 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2">
+        <v>1001</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="str">
+        <f>CONCATENATE("CODING &amp; AI"," ( ",E2," )")</f>
+        <v>CODING &amp; AI ( X AKL 1 )</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -535,9 +661,18 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3">
+        <v>1002</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F30" si="0">CONCATENATE("CODING &amp; AI"," ( ",E3," )")</f>
+        <v>CODING &amp; AI ( X AKL 2 )</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -547,9 +682,18 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <v>1003</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X PM )</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -559,9 +703,18 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5">
+        <v>1004</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X MPLB 1 )</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -571,9 +724,18 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6">
+        <v>1005</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X MPLB 2 )</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -583,9 +745,18 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7">
+        <v>1006</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X TJKT 1 )</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -595,9 +766,18 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <v>1007</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X TJKT 2 )</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -607,9 +787,18 @@
       <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <v>1008</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X TJKT 3 )</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -619,9 +808,18 @@
       <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <v>1009</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X TJKT 4 )</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -631,7 +829,415 @@
       <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11">
+        <v>1010</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( X DKV )</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12">
+        <v>1011</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI AKL 1 )</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13">
+        <v>1012</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI AKL 2 )</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14">
+        <v>1013</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI PM )</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15">
+        <v>1014</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI MPLB 1 )</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1015</v>
+      </c>
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16">
+        <v>1015</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI MPLB 2 )</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1016</v>
+      </c>
+      <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>1016</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI TJKT 1 )</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1017</v>
+      </c>
+      <c r="B18">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>1017</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI TJKT 2 )</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1018</v>
+      </c>
+      <c r="B19">
+        <v>1018</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19">
+        <v>1018</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI TJKT 3 )</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1019</v>
+      </c>
+      <c r="B20">
+        <v>1019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20">
+        <v>1019</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI TJKT 4 )</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1020</v>
+      </c>
+      <c r="B21">
+        <v>1020</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21">
+        <v>1020</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XI DKV )</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1021</v>
+      </c>
+      <c r="B22">
+        <v>1021</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22">
+        <v>1021</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII AKL 1 )</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1022</v>
+      </c>
+      <c r="B23">
+        <v>1022</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23">
+        <v>1022</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII AKL 2 )</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1023</v>
+      </c>
+      <c r="B24">
+        <v>1023</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24">
+        <v>1023</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII PM )</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25">
+        <v>1024</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25">
+        <v>1024</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII MPLB 1 )</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>1025</v>
+      </c>
+      <c r="B26">
+        <v>1025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26">
+        <v>1025</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII MPLB 2 )</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>1026</v>
+      </c>
+      <c r="B27">
+        <v>1026</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27">
+        <v>1026</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII TJKT 1 )</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1027</v>
+      </c>
+      <c r="B28">
+        <v>1027</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28">
+        <v>1027</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII TJKT 2 )</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1028</v>
+      </c>
+      <c r="B29">
+        <v>1028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29">
+        <v>1028</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII TJKT 3 )</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1029</v>
+      </c>
+      <c r="B30">
+        <v>1029</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30">
+        <v>1029</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>CODING &amp; AI ( XII DKV )</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
